--- a/attendance/templates/student_template.xlsx
+++ b/attendance/templates/student_template.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\myapp\myproject\attendance\templates\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="20115" windowHeight="8505"/>
   </bookViews>
@@ -24,9 +29,6 @@
     <t>Roll Number</t>
   </si>
   <si>
-    <t>Class</t>
-  </si>
-  <si>
     <t>Section</t>
   </si>
   <si>
@@ -49,13 +51,16 @@
   </si>
   <si>
     <t>a</t>
+  </si>
+  <si>
+    <t>student_class</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -74,6 +79,12 @@
       <color rgb="FFECECEC"/>
       <name val="Segoe UI"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9CDCFE"/>
+      <name val="Consolas"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="3">
@@ -154,7 +165,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -168,6 +179,9 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -177,6 +191,9 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -225,7 +242,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -260,7 +277,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -471,6 +488,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="21.85546875" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
@@ -479,16 +499,16 @@
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>2</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B2" s="3">
         <v>1</v>
@@ -497,12 +517,12 @@
         <v>10</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B3" s="3">
         <v>2</v>
@@ -511,12 +531,12 @@
         <v>10</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B4" s="1">
         <v>3</v>
@@ -525,12 +545,12 @@
         <v>10</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B5" s="3">
         <v>4</v>
@@ -539,12 +559,12 @@
         <v>10</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6" s="3">
         <v>5</v>
@@ -553,12 +573,12 @@
         <v>10</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B7" s="1">
         <v>6</v>
@@ -567,7 +587,7 @@
         <v>10</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/attendance/templates/student_template.xlsx
+++ b/attendance/templates/student_template.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\myapp\myproject\attendance\templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\StudioProjects\myproject\attendance\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -21,46 +21,40 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="9">
   <si>
     <t>Name</t>
   </si>
   <si>
-    <t>Roll Number</t>
-  </si>
-  <si>
     <t>Section</t>
   </si>
   <si>
-    <t>John Doe</t>
-  </si>
-  <si>
     <t>A</t>
   </si>
   <si>
-    <t>Jane Smith</t>
-  </si>
-  <si>
-    <t>B</t>
-  </si>
-  <si>
-    <t>ramu</t>
-  </si>
-  <si>
-    <t>raj</t>
-  </si>
-  <si>
-    <t>a</t>
-  </si>
-  <si>
     <t>student_class</t>
+  </si>
+  <si>
+    <t>Mano</t>
+  </si>
+  <si>
+    <t>vignesh</t>
+  </si>
+  <si>
+    <t>Balaji</t>
+  </si>
+  <si>
+    <t>jothi</t>
+  </si>
+  <si>
+    <t>abi</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -69,39 +63,28 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9.6"/>
-      <color rgb="FFECECEC"/>
-      <name val="Segoe UI"/>
-      <family val="2"/>
+      <b/>
+      <sz val="13"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
-      <sz val="9.6"/>
-      <color rgb="FFECECEC"/>
-      <name val="Segoe UI"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9CDCFE"/>
-      <name val="Consolas"/>
-      <family val="3"/>
+      <sz val="13"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF212121"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="5">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -111,53 +94,16 @@
     </border>
     <border>
       <left style="medium">
-        <color rgb="FF000000"/>
+        <color rgb="FFBBBBBB"/>
       </left>
-      <right/>
+      <right style="medium">
+        <color rgb="FFBBBBBB"/>
+      </right>
       <top style="medium">
-        <color rgb="FF000000"/>
+        <color rgb="FFBBBBBB"/>
       </top>
       <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
+        <color rgb="FFBBBBBB"/>
       </bottom>
       <diagonal/>
     </border>
@@ -165,22 +111,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -486,108 +423,82 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="21.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="1"/>
+      <c r="C1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2">
+        <v>11</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="3">
-        <v>1</v>
-      </c>
-      <c r="C2" s="3">
-        <v>10</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>4</v>
+    <row r="3" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2">
+        <v>11</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="3">
+    <row r="4" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2">
+        <v>11</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="3">
-        <v>10</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>6</v>
-      </c>
     </row>
-    <row r="4" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
+    <row r="5" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="1">
-        <v>3</v>
-      </c>
-      <c r="C4" s="1">
-        <v>10</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>9</v>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2">
+        <v>11</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="3">
-        <v>4</v>
-      </c>
-      <c r="C5" s="3">
-        <v>10</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6" s="3">
-        <v>5</v>
-      </c>
-      <c r="C6" s="3">
-        <v>10</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
+    <row r="6" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="1">
-        <v>6</v>
-      </c>
-      <c r="C7" s="1">
-        <v>10</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>9</v>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2">
+        <v>11</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
